--- a/Result/checksun_f/2025-11-21.xlsx
+++ b/Result/checksun_f/2025-11-21.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d1】;【d2】;【x】看好</t>
+          <t>【d1】;【x】看好</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1058,15 +1058,11 @@
           <t>190.6</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>186.3</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>207.78</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>186.3</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>207.78</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1304,7 +1300,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1489,15 +1485,11 @@
           <t>191.4</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>186.98</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>208.76</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>186.98</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>208.76</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1735,7 +1727,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1920,15 +1912,11 @@
           <t>192.1</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>187.72</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>209.75</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>187.72</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>209.75</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -2166,7 +2154,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2351,15 +2339,11 @@
           <t>193.4</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>188.55</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>210.8</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>188.55</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>210.8</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2597,7 +2581,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2782,15 +2766,11 @@
           <t>193.7</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>189.3</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>211.76</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>189.3</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>211.76</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -3028,7 +3008,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3213,15 +3193,11 @@
           <t>192.9</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>190.02</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>212.73</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>190.02</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>212.73</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3459,7 +3435,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3644,15 +3620,11 @@
           <t>193.8</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>191.02</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>213.64</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>191.02</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>213.64</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3890,7 +3862,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4075,15 +4047,11 @@
           <t>192.2</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>191.62</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>214.64</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>191.62</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>214.64</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4319,7 +4287,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>8069</t>
@@ -4502,15 +4474,11 @@
           <t>187.1</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>192.22</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>215.57</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>192.22</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>215.57</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4746,7 +4714,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>8069</t>
@@ -4929,15 +4901,11 @@
           <t>182.6</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>193.0</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>216.61</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>193</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>216.61</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5173,7 +5141,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>8069</t>
@@ -5356,15 +5328,11 @@
           <t>179.4</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>194.1</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>217.7</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>194.1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>217.7</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5788,15 +5756,11 @@
           <t>62.1</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>58.04</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>50.89</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>58.04</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>50.89</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -6220,15 +6184,11 @@
           <t>63.08</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>57.38</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>50.56</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>57.38</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>50.56</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6652,15 +6612,11 @@
           <t>64.64000000000001</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>56.74</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>50.24</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>56.74</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>50.24</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -7084,15 +7040,11 @@
           <t>65.08000000000001</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>55.77</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>49.86</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>55.77</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>49.86</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7516,15 +7468,11 @@
           <t>65.52000000000001</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>54.82</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>49.47</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>54.82</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>49.47</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7948,15 +7896,11 @@
           <t>66.26</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>53.89</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>49.04</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>53.89</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>49.04</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8380,15 +8324,11 @@
           <t>65.8</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>52.88</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>48.59</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>52.88</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>48.59</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8812,15 +8752,11 @@
           <t>64.02000000000001</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>51.74</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>48.08</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>51.74</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>48.08</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -9244,15 +9180,11 @@
           <t>61.67999999999999</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>50.72</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>47.62</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>47.62</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9676,15 +9608,11 @@
           <t>59.38</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>47.16</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>47.16</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -10108,15 +10036,11 @@
           <t>56.42</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>48.61</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>46.65</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>48.61</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>46.65</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10538,15 +10462,11 @@
           <t>82.76</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>71.21</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>54.67</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>71.20999999999999</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>54.67</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10968,15 +10888,11 @@
           <t>81.08</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>69.18</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>53.63</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>69.18000000000001</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>53.63</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11398,15 +11314,11 @@
           <t>79.4</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>67.4</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>52.59</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>52.59</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11828,15 +11740,11 @@
           <t>77.38</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>65.38</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>51.47</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>65.38</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>51.47</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12258,15 +12166,11 @@
           <t>77.06</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>63.79</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>50.48</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>63.79</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>50.48</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12688,15 +12592,11 @@
           <t>77.96000000000001</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>62.22</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>49.46</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>62.22</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>49.46</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -13118,15 +13018,11 @@
           <t>78.34</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>60.68</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>48.42</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>60.68</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>48.42</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13548,15 +13444,11 @@
           <t>77.86</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>59.32</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>47.44</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>59.32</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>47.44</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13978,15 +13870,11 @@
           <t>76.14</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>58.0</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>46.46</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>58</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>46.46</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14408,15 +14296,11 @@
           <t>73.82000000000001</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>56.76</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>45.48</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>56.76</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>45.48</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14838,15 +14722,11 @@
           <t>68.74000000000001</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>55.25</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>44.32</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>55.25</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>44.32</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15268,15 +15148,11 @@
           <t>57.0</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>49.79</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>45.08</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>49.79</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>45.08</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15698,15 +15574,11 @@
           <t>56.98</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>48.9</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>44.69</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>44.69</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -16128,15 +16000,11 @@
           <t>55.8</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>48.04</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>44.31</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>48.04</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>44.31</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16558,15 +16426,11 @@
           <t>54.02</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>47.06</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>43.91</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>47.06</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>43.91</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16988,15 +16852,11 @@
           <t>53.76000000000001</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>46.38</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>43.55</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>46.38</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>43.55</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17418,15 +17278,11 @@
           <t>53.73999999999999</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>45.69</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>43.09</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>45.69</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>43.09</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17848,15 +17704,11 @@
           <t>52.48</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>44.98</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>42.58</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>44.98</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>42.58</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18278,15 +18130,11 @@
           <t>51.35</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>44.56</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>42.2</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>44.56</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>42.2</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18708,15 +18556,11 @@
           <t>50.31</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>44.27</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>41.82</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>44.27</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>41.82</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -19138,15 +18982,11 @@
           <t>48.01000000000001</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>43.98</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>41.41</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>41.41</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19568,15 +19408,11 @@
           <t>45.33</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>43.68</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>40.95</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>43.68</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>40.95</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19998,15 +19834,11 @@
           <t>284.8</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>260.27</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>241.07</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>260.27</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>241.07</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20428,15 +20260,11 @@
           <t>282.5</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>257.23</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>239.87</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>257.23</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>239.87</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20858,15 +20686,11 @@
           <t>281.3</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>254.18</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>238.82</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>254.18</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>238.82</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21288,15 +21112,11 @@
           <t>283.0</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>251.8</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>237.69</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>251.8</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>237.69</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21718,15 +21538,11 @@
           <t>282.0</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>249.0</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>236.21</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>249</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>236.21</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22148,15 +21964,11 @@
           <t>280.9</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>245.55</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>234.63</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>245.55</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>234.63</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22578,15 +22390,11 @@
           <t>279.4</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>242.88</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>233.36</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>242.88</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>233.36</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -23008,15 +22816,11 @@
           <t>271.3</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>239.98</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>231.93</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>239.98</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>231.93</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23438,15 +23242,11 @@
           <t>262.1</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>236.68</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>230.33</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>236.68</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>230.33</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23868,15 +23668,11 @@
           <t>251.8</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>233.7</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>228.97</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>233.7</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>228.97</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24298,15 +24094,11 @@
           <t>243.5</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>230.98</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>227.78</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>230.98</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>227.78</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24542,7 +24334,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>6743</t>
@@ -24726,15 +24522,11 @@
           <t>29.15</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>29.17</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>29.91</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>29.91</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -24972,7 +24764,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25158,15 +24950,11 @@
           <t>29.27</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>29.2</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>30</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25404,7 +25192,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25590,15 +25378,11 @@
           <t>29.34</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>29.22</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>30.09</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>29.22</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>30.09</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25836,7 +25620,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26022,15 +25806,11 @@
           <t>29.43</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>29.2</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>30.2</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>30.2</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26268,7 +26048,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26454,15 +26234,11 @@
           <t>29.59</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>29.18</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>30.31</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>29.18</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>30.31</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26700,7 +26476,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -26886,15 +26662,11 @@
           <t>29.5</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>29.17</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>30.42</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>30.42</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27132,7 +26904,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27318,15 +27090,11 @@
           <t>29.56</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>29.16</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>30.5</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>29.16</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>30.5</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27564,7 +27332,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -27750,15 +27518,11 @@
           <t>29.36</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>29.18</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>30.57</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>29.18</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>30.57</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -27994,7 +27758,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>6743</t>
@@ -28178,15 +27946,11 @@
           <t>29.01</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>29.18</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>30.64</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>29.18</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>30.64</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28422,7 +28186,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>6743</t>
@@ -28606,15 +28374,11 @@
           <t>28.67</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>29.16</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>30.71</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>29.16</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>30.71</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -28850,7 +28614,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>6743</t>
@@ -29034,15 +28802,11 @@
           <t>28.52</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>29.22</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>30.82</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>29.22</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>30.82</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29464,15 +29228,11 @@
           <t>130.0</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>131.18</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>127.36</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>131.18</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>127.36</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29894,15 +29654,11 @@
           <t>132.2</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>132.57</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>127.2</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>132.57</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>127.2</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,15 +30080,11 @@
           <t>133.0</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>133.82</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>126.98</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>133.82</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>126.98</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30754,15 +30506,11 @@
           <t>132.7</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>134.38</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>126.72</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>134.38</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>126.72</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31184,15 +30932,11 @@
           <t>131.8</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>134.85</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>126.42</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>134.85</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>126.42</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31614,15 +31358,11 @@
           <t>131.6</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>135.28</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>126.21</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>135.28</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>126.21</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32044,15 +31784,11 @@
           <t>130.1</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>135.12</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>125.89</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>135.12</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>125.89</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32474,15 +32210,11 @@
           <t>128.2</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>134.8</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>125.54</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>125.54</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32904,15 +32636,11 @@
           <t>126.7</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>134.52</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>125.14</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>134.52</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>125.14</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33334,15 +33062,11 @@
           <t>126.7</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>134.43</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>124.81</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>134.43</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>124.81</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33764,15 +33488,11 @@
           <t>126.7</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>134.15</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>124.4</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>134.15</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>124.4</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34194,15 +33914,11 @@
           <t>175.7</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>158.68</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>150.48</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>158.68</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>150.48</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34624,15 +34340,11 @@
           <t>174.3</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>156.1</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>150.26</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>156.1</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>150.26</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35054,15 +34766,11 @@
           <t>172.6</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>153.57</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>149.87</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>153.57</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>149.87</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35484,15 +35192,11 @@
           <t>172.0</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>151.02</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>149.56</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>151.02</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>149.56</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35730,7 +35434,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -35914,15 +35618,11 @@
           <t>173.3</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>149.05</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>149.52</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>149.05</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>149.52</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36160,7 +35860,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36344,15 +36044,11 @@
           <t>172.6</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>146.98</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>149.49</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>146.98</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>149.49</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36590,7 +36286,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -36774,15 +36470,11 @@
           <t>169.9</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>145.12</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>149.71</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>145.12</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>149.71</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37020,7 +36712,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37204,15 +36896,11 @@
           <t>164.4</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>143.3</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>150.07</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>143.3</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>150.07</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37450,7 +37138,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -37634,15 +37322,11 @@
           <t>156.2</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>141.4</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>150.51</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>141.4</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>150.51</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -37880,7 +37564,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38064,15 +37748,11 @@
           <t>147.7</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>139.45</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>150.97</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>139.45</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>150.97</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38310,7 +37990,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38494,15 +38174,11 @@
           <t>142.6</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>137.9</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>151.6</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>137.9</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>151.6</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -38738,7 +38414,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>4804</t>
@@ -38920,15 +38600,11 @@
           <t>7.404000000000001</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>7.46</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>8.220000000000001</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39164,7 +38840,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>4804</t>
@@ -39346,15 +39026,11 @@
           <t>7.364</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>7.53</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>8.26</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>8.26</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39590,7 +39266,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>4804</t>
@@ -39772,15 +39452,11 @@
           <t>7.165999999999999</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>7.57</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>8.29</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>8.289999999999999</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40016,7 +39692,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>4804</t>
@@ -40198,15 +39878,11 @@
           <t>7.145999999999999</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>7.61</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>8.33</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>8.33</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40442,7 +40118,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>4804</t>
@@ -40624,15 +40304,11 @@
           <t>7.146000000000001</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>7.67</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>8.38</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>8.380000000000001</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41054,15 +40730,11 @@
           <t>7.202</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>7.69</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>8.43</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>8.43</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41484,15 +41156,11 @@
           <t>7.290000000000001</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>7.71</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>8.48</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>8.48</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -41914,15 +41582,11 @@
           <t>7.292</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>7.73</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>8.54</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>8.539999999999999</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42344,15 +42008,11 @@
           <t>7.405999999999999</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>7.75</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>8.6</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>8.6</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42588,7 +42248,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>4804</t>
@@ -42770,15 +42434,11 @@
           <t>7.548</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>7.76</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>8.65</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>8.65</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43200,15 +42860,11 @@
           <t>7.597999999999999</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>7.79</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>8.7</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43630,15 +43286,11 @@
           <t>25.3</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>21.46</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>18.44</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>21.46</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>18.44</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44060,15 +43712,11 @@
           <t>24.92</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>20.93</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>18.24</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>20.93</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>18.24</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44490,15 +44138,11 @@
           <t>24.66</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>20.45</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>18.06</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>18.06</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -44920,15 +44564,11 @@
           <t>24.47</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>20.02</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>17.89</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>17.89</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45350,15 +44990,11 @@
           <t>24.37</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>19.62</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>17.73</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>19.62</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>17.73</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -45780,15 +45416,11 @@
           <t>23.78</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>17.56</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>17.56</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46210,15 +45842,11 @@
           <t>23.02</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>18.77</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>17.39</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>17.39</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46640,15 +46268,11 @@
           <t>21.92</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>18.36</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>17.22</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>17.22</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47070,15 +46694,11 @@
           <t>20.64</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>17.97</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>17.07</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>17.07</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47500,15 +47120,11 @@
           <t>19.35</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>17.59</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>16.92</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>16.92</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -47930,15 +47546,11 @@
           <t>18.69</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>17.32</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>16.82</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>16.82</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48360,15 +47972,11 @@
           <t>33.09</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>33.06</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>33.15</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>33.06</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>33.15</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -48606,7 +48214,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -48790,15 +48398,11 @@
           <t>33.34</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>33.19</t>
-        </is>
+      <c r="AM113" t="n">
+        <v>33.05</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>33.19</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -49036,7 +48640,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49220,15 +48824,11 @@
           <t>33.46</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>33.02</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>33.22</t>
-        </is>
+      <c r="AM114" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>33.22</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -49466,7 +49066,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -49650,15 +49250,11 @@
           <t>33.63</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>33.01</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>33.26</t>
-        </is>
+      <c r="AM115" t="n">
+        <v>33.01</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>33.26</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -49896,7 +49492,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -50080,15 +49676,11 @@
           <t>33.73999999999999</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>32.99</t>
-        </is>
-      </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>33.3</t>
-        </is>
+      <c r="AM116" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>33.3</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -50326,7 +49918,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -50510,15 +50102,11 @@
           <t>33.53</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>32.92</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>33.3</t>
-        </is>
+      <c r="AM117" t="n">
+        <v>32.92</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>33.3</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -50756,7 +50344,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -50940,15 +50528,11 @@
           <t>33.54</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>32.85</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>33.31</t>
-        </is>
+      <c r="AM118" t="n">
+        <v>32.85</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>33.31</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -51186,7 +50770,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -51370,15 +50954,11 @@
           <t>33.3</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>32.78</t>
-        </is>
-      </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>33.33</t>
-        </is>
+      <c r="AM119" t="n">
+        <v>32.78</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>33.33</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -51616,7 +51196,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -51800,15 +51380,11 @@
           <t>33.0</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>32.72</t>
-        </is>
-      </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>33.35</t>
-        </is>
+      <c r="AM120" t="n">
+        <v>32.72</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>33.35</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -52046,7 +51622,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -52230,15 +51806,11 @@
           <t>32.73999999999999</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>32.71</t>
-        </is>
-      </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>33.37</t>
-        </is>
+      <c r="AM121" t="n">
+        <v>32.71</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>33.37</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -52474,7 +52046,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr"/>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>4735</t>
@@ -52656,15 +52232,11 @@
           <t>32.66</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>32.72</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>33.4</t>
-        </is>
+      <c r="AM122" t="n">
+        <v>32.72</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>33.4</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -53086,15 +52658,11 @@
           <t>12.4</t>
         </is>
       </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>11.64</t>
-        </is>
-      </c>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>11.37</t>
-        </is>
+      <c r="AM123" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>11.37</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -53516,15 +53084,11 @@
           <t>12.46</t>
         </is>
       </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>11.55</t>
-        </is>
-      </c>
-      <c r="AN124" t="inlineStr">
-        <is>
-          <t>11.36</t>
-        </is>
+      <c r="AM124" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>11.36</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -53946,15 +53510,11 @@
           <t>12.57</t>
         </is>
       </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>11.46</t>
-        </is>
-      </c>
-      <c r="AN125" t="inlineStr">
-        <is>
-          <t>11.34</t>
-        </is>
+      <c r="AM125" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>11.34</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -54376,15 +53936,11 @@
           <t>12.6</t>
         </is>
       </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>11.37</t>
-        </is>
-      </c>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>11.33</t>
-        </is>
+      <c r="AM126" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>11.33</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -54622,7 +54178,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -54806,15 +54362,11 @@
           <t>12.59</t>
         </is>
       </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>11.3</t>
-        </is>
-      </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>11.32</t>
-        </is>
+      <c r="AM127" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>11.32</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
@@ -55052,7 +54604,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -55236,15 +54788,11 @@
           <t>12.38</t>
         </is>
       </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>11.23</t>
-        </is>
-      </c>
-      <c r="AN128" t="inlineStr">
-        <is>
-          <t>11.3</t>
-        </is>
+      <c r="AM128" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>11.3</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -55482,7 +55030,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -55666,15 +55214,11 @@
           <t>12.14</t>
         </is>
       </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>11.16</t>
-        </is>
-      </c>
-      <c r="AN129" t="inlineStr">
-        <is>
-          <t>11.27</t>
-        </is>
+      <c r="AM129" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>11.27</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -55912,7 +55456,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -56096,15 +55640,11 @@
           <t>11.67</t>
         </is>
       </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="AN130" t="inlineStr">
-        <is>
-          <t>11.25</t>
-        </is>
+      <c r="AM130" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>11.25</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -56342,7 +55882,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -56526,15 +56066,11 @@
           <t>11.28</t>
         </is>
       </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>11.02</t>
-        </is>
-      </c>
-      <c r="AN131" t="inlineStr">
-        <is>
-          <t>11.23</t>
-        </is>
+      <c r="AM131" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>11.23</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -56772,7 +56308,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -56956,15 +56492,11 @@
           <t>11.01</t>
         </is>
       </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>10.98</t>
-        </is>
-      </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>11.21</t>
-        </is>
+      <c r="AM132" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>11.21</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -57200,7 +56732,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr"/>
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>4530</t>
@@ -57382,15 +56918,11 @@
           <t>10.9</t>
         </is>
       </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>10.96</t>
-        </is>
-      </c>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>11.22</t>
-        </is>
+      <c r="AM133" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>11.22</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -57628,7 +57160,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -57813,15 +57345,11 @@
           <t>26.03</t>
         </is>
       </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>25.86</t>
-        </is>
-      </c>
-      <c r="AN134" t="inlineStr">
-        <is>
-          <t>26.64</t>
-        </is>
+      <c r="AM134" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>26.64</v>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
@@ -58059,7 +57587,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -58244,15 +57772,11 @@
           <t>26.15</t>
         </is>
       </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>25.83</t>
-        </is>
-      </c>
-      <c r="AN135" t="inlineStr">
-        <is>
-          <t>26.66</t>
-        </is>
+      <c r="AM135" t="n">
+        <v>25.83</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>26.66</v>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
@@ -58490,7 +58014,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -58675,15 +58199,11 @@
           <t>26.16</t>
         </is>
       </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>25.87</t>
-        </is>
-      </c>
-      <c r="AN136" t="inlineStr">
-        <is>
-          <t>26.67</t>
-        </is>
+      <c r="AM136" t="n">
+        <v>25.87</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>26.67</v>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
@@ -58921,7 +58441,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -59106,15 +58626,11 @@
           <t>26.28</t>
         </is>
       </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>25.95</t>
-        </is>
-      </c>
-      <c r="AN137" t="inlineStr">
-        <is>
-          <t>26.69</t>
-        </is>
+      <c r="AM137" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>26.69</v>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
@@ -59352,7 +58868,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -59537,15 +59053,11 @@
           <t>26.11</t>
         </is>
       </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>25.97</t>
-        </is>
-      </c>
-      <c r="AN138" t="inlineStr">
-        <is>
-          <t>26.69</t>
-        </is>
+      <c r="AM138" t="n">
+        <v>25.97</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>26.69</v>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
@@ -59781,7 +59293,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr"/>
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>4192</t>
@@ -59964,15 +59480,11 @@
           <t>25.92</t>
         </is>
       </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="AN139" t="inlineStr">
-        <is>
-          <t>26.69</t>
-        </is>
+      <c r="AM139" t="n">
+        <v>26</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>26.69</v>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
@@ -60208,7 +59720,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr"/>
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>4192</t>
@@ -60391,15 +59907,11 @@
           <t>25.92</t>
         </is>
       </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>26.07</t>
-        </is>
-      </c>
-      <c r="AN140" t="inlineStr">
-        <is>
-          <t>26.7</t>
-        </is>
+      <c r="AM140" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>26.7</v>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
@@ -60635,7 +60147,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr"/>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>4192</t>
@@ -60818,15 +60334,11 @@
           <t>25.71</t>
         </is>
       </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>26.11</t>
-        </is>
-      </c>
-      <c r="AN141" t="inlineStr">
-        <is>
-          <t>26.73</t>
-        </is>
+      <c r="AM141" t="n">
+        <v>26.11</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>26.73</v>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
@@ -61249,15 +60761,11 @@
           <t>25.48</t>
         </is>
       </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>26.13</t>
-        </is>
-      </c>
-      <c r="AN142" t="inlineStr">
-        <is>
-          <t>26.73</t>
-        </is>
+      <c r="AM142" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>26.73</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
@@ -61680,15 +61188,11 @@
           <t>25.35</t>
         </is>
       </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>26.16</t>
-        </is>
-      </c>
-      <c r="AN143" t="inlineStr">
-        <is>
-          <t>26.74</t>
-        </is>
+      <c r="AM143" t="n">
+        <v>26.16</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>26.74</v>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
@@ -62111,15 +61615,11 @@
           <t>25.38</t>
         </is>
       </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>26.27</t>
-        </is>
-      </c>
-      <c r="AN144" t="inlineStr">
-        <is>
-          <t>26.77</t>
-        </is>
+      <c r="AM144" t="n">
+        <v>26.27</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>26.77</v>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
@@ -62542,15 +62042,11 @@
           <t>48.82</t>
         </is>
       </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>48.48</t>
-        </is>
-      </c>
-      <c r="AN145" t="inlineStr">
-        <is>
-          <t>43.84</t>
-        </is>
+      <c r="AM145" t="n">
+        <v>48.48</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>43.84</v>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
@@ -62973,15 +62469,11 @@
           <t>49.39</t>
         </is>
       </c>
-      <c r="AM146" t="inlineStr">
-        <is>
-          <t>48.03</t>
-        </is>
-      </c>
-      <c r="AN146" t="inlineStr">
-        <is>
-          <t>43.68</t>
-        </is>
+      <c r="AM146" t="n">
+        <v>48.03</v>
+      </c>
+      <c r="AN146" t="n">
+        <v>43.68</v>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
@@ -63404,15 +62896,11 @@
           <t>49.77</t>
         </is>
       </c>
-      <c r="AM147" t="inlineStr">
-        <is>
-          <t>47.61</t>
-        </is>
-      </c>
-      <c r="AN147" t="inlineStr">
-        <is>
-          <t>43.52</t>
-        </is>
+      <c r="AM147" t="n">
+        <v>47.61</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>43.52</v>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
@@ -63835,15 +63323,11 @@
           <t>49.46</t>
         </is>
       </c>
-      <c r="AM148" t="inlineStr">
-        <is>
-          <t>47.13</t>
-        </is>
-      </c>
-      <c r="AN148" t="inlineStr">
-        <is>
-          <t>43.33</t>
-        </is>
+      <c r="AM148" t="n">
+        <v>47.13</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>43.33</v>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
@@ -64266,15 +63750,11 @@
           <t>49.75000000000001</t>
         </is>
       </c>
-      <c r="AM149" t="inlineStr">
-        <is>
-          <t>46.76</t>
-        </is>
-      </c>
-      <c r="AN149" t="inlineStr">
-        <is>
-          <t>43.13</t>
-        </is>
+      <c r="AM149" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>43.13</v>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
@@ -64697,15 +64177,11 @@
           <t>50.47000000000001</t>
         </is>
       </c>
-      <c r="AM150" t="inlineStr">
-        <is>
-          <t>46.41</t>
-        </is>
-      </c>
-      <c r="AN150" t="inlineStr">
-        <is>
-          <t>42.91</t>
-        </is>
+      <c r="AM150" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="AN150" t="n">
+        <v>42.91</v>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
@@ -65128,15 +64604,11 @@
           <t>50.73</t>
         </is>
       </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>45.94</t>
-        </is>
-      </c>
-      <c r="AN151" t="inlineStr">
-        <is>
-          <t>42.62</t>
-        </is>
+      <c r="AM151" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="AN151" t="n">
+        <v>42.62</v>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
@@ -65559,15 +65031,11 @@
           <t>50.69</t>
         </is>
       </c>
-      <c r="AM152" t="inlineStr">
-        <is>
-          <t>45.54</t>
-        </is>
-      </c>
-      <c r="AN152" t="inlineStr">
-        <is>
-          <t>42.36</t>
-        </is>
+      <c r="AM152" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>42.36</v>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
@@ -65990,15 +65458,11 @@
           <t>51.56</t>
         </is>
       </c>
-      <c r="AM153" t="inlineStr">
-        <is>
-          <t>45.43</t>
-        </is>
-      </c>
-      <c r="AN153" t="inlineStr">
-        <is>
-          <t>42.13</t>
-        </is>
+      <c r="AM153" t="n">
+        <v>45.43</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>42.13</v>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
@@ -66421,15 +65885,11 @@
           <t>51.13</t>
         </is>
       </c>
-      <c r="AM154" t="inlineStr">
-        <is>
-          <t>45.26</t>
-        </is>
-      </c>
-      <c r="AN154" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
+      <c r="AM154" t="n">
+        <v>45.26</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>41.9</v>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
@@ -66852,15 +66312,11 @@
           <t>50.01</t>
         </is>
       </c>
-      <c r="AM155" t="inlineStr">
-        <is>
-          <t>45.04</t>
-        </is>
-      </c>
-      <c r="AN155" t="inlineStr">
-        <is>
-          <t>41.6</t>
-        </is>
+      <c r="AM155" t="n">
+        <v>45.04</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>41.6</v>
       </c>
       <c r="AO155" t="inlineStr">
         <is>
@@ -67282,15 +66738,11 @@
           <t>27.62</t>
         </is>
       </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>23.22</t>
-        </is>
-      </c>
-      <c r="AN156" t="inlineStr">
-        <is>
-          <t>21.01</t>
-        </is>
+      <c r="AM156" t="n">
+        <v>23.22</v>
+      </c>
+      <c r="AN156" t="n">
+        <v>21.01</v>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
@@ -67712,15 +67164,11 @@
           <t>27.42</t>
         </is>
       </c>
-      <c r="AM157" t="inlineStr">
-        <is>
-          <t>22.78</t>
-        </is>
-      </c>
-      <c r="AN157" t="inlineStr">
-        <is>
-          <t>20.86</t>
-        </is>
+      <c r="AM157" t="n">
+        <v>22.78</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>20.86</v>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
@@ -68142,15 +67590,11 @@
           <t>26.89</t>
         </is>
       </c>
-      <c r="AM158" t="inlineStr">
-        <is>
-          <t>22.37</t>
-        </is>
-      </c>
-      <c r="AN158" t="inlineStr">
-        <is>
-          <t>20.68</t>
-        </is>
+      <c r="AM158" t="n">
+        <v>22.37</v>
+      </c>
+      <c r="AN158" t="n">
+        <v>20.68</v>
       </c>
       <c r="AO158" t="inlineStr">
         <is>
@@ -68572,15 +68016,11 @@
           <t>26.37</t>
         </is>
       </c>
-      <c r="AM159" t="inlineStr">
-        <is>
-          <t>21.96</t>
-        </is>
-      </c>
-      <c r="AN159" t="inlineStr">
-        <is>
-          <t>20.51</t>
-        </is>
+      <c r="AM159" t="n">
+        <v>21.96</v>
+      </c>
+      <c r="AN159" t="n">
+        <v>20.51</v>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
@@ -69002,15 +68442,11 @@
           <t>25.95</t>
         </is>
       </c>
-      <c r="AM160" t="inlineStr">
-        <is>
-          <t>21.58</t>
-        </is>
-      </c>
-      <c r="AN160" t="inlineStr">
-        <is>
-          <t>20.34</t>
-        </is>
+      <c r="AM160" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="AN160" t="n">
+        <v>20.34</v>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
@@ -69432,15 +68868,11 @@
           <t>25.55</t>
         </is>
       </c>
-      <c r="AM161" t="inlineStr">
-        <is>
-          <t>21.23</t>
-        </is>
-      </c>
-      <c r="AN161" t="inlineStr">
-        <is>
-          <t>20.18</t>
-        </is>
+      <c r="AM161" t="n">
+        <v>21.23</v>
+      </c>
+      <c r="AN161" t="n">
+        <v>20.18</v>
       </c>
       <c r="AO161" t="inlineStr">
         <is>
@@ -69862,15 +69294,11 @@
           <t>24.69</t>
         </is>
       </c>
-      <c r="AM162" t="inlineStr">
-        <is>
-          <t>20.88</t>
-        </is>
-      </c>
-      <c r="AN162" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
+      <c r="AM162" t="n">
+        <v>20.88</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>20</v>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
@@ -70292,15 +69720,11 @@
           <t>23.76</t>
         </is>
       </c>
-      <c r="AM163" t="inlineStr">
-        <is>
-          <t>20.62</t>
-        </is>
-      </c>
-      <c r="AN163" t="inlineStr">
-        <is>
-          <t>19.88</t>
-        </is>
+      <c r="AM163" t="n">
+        <v>20.62</v>
+      </c>
+      <c r="AN163" t="n">
+        <v>19.88</v>
       </c>
       <c r="AO163" t="inlineStr">
         <is>
@@ -70722,15 +70146,11 @@
           <t>22.56</t>
         </is>
       </c>
-      <c r="AM164" t="inlineStr">
-        <is>
-          <t>20.35</t>
-        </is>
-      </c>
-      <c r="AN164" t="inlineStr">
-        <is>
-          <t>19.75</t>
-        </is>
+      <c r="AM164" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="AN164" t="n">
+        <v>19.75</v>
       </c>
       <c r="AO164" t="inlineStr">
         <is>
@@ -71152,15 +70572,11 @@
           <t>21.38</t>
         </is>
       </c>
-      <c r="AM165" t="inlineStr">
-        <is>
-          <t>20.1</t>
-        </is>
-      </c>
-      <c r="AN165" t="inlineStr">
-        <is>
-          <t>19.63</t>
-        </is>
+      <c r="AM165" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="AN165" t="n">
+        <v>19.63</v>
       </c>
       <c r="AO165" t="inlineStr">
         <is>
@@ -71582,15 +70998,11 @@
           <t>20.25</t>
         </is>
       </c>
-      <c r="AM166" t="inlineStr">
-        <is>
-          <t>19.89</t>
-        </is>
-      </c>
-      <c r="AN166" t="inlineStr">
-        <is>
-          <t>19.51</t>
-        </is>
+      <c r="AM166" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="AN166" t="n">
+        <v>19.51</v>
       </c>
       <c r="AO166" t="inlineStr">
         <is>
@@ -71826,7 +71238,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr"/>
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>3297</t>
@@ -72010,15 +71426,11 @@
           <t>42.89</t>
         </is>
       </c>
-      <c r="AM167" t="inlineStr">
-        <is>
-          <t>44.62</t>
-        </is>
-      </c>
-      <c r="AN167" t="inlineStr">
-        <is>
-          <t>48.08</t>
-        </is>
+      <c r="AM167" t="n">
+        <v>44.62</v>
+      </c>
+      <c r="AN167" t="n">
+        <v>48.08</v>
       </c>
       <c r="AO167" t="inlineStr">
         <is>
@@ -72254,7 +71666,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr"/>
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>3297</t>
@@ -72438,15 +71854,11 @@
           <t>43.15</t>
         </is>
       </c>
-      <c r="AM168" t="inlineStr">
-        <is>
-          <t>44.78</t>
-        </is>
-      </c>
-      <c r="AN168" t="inlineStr">
-        <is>
-          <t>48.4</t>
-        </is>
+      <c r="AM168" t="n">
+        <v>44.78</v>
+      </c>
+      <c r="AN168" t="n">
+        <v>48.4</v>
       </c>
       <c r="AO168" t="inlineStr">
         <is>
@@ -72682,7 +72094,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr"/>
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>3297</t>
@@ -72866,15 +72282,11 @@
           <t>43.27</t>
         </is>
       </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>44.98</t>
-        </is>
-      </c>
-      <c r="AN169" t="inlineStr">
-        <is>
-          <t>48.73</t>
-        </is>
+      <c r="AM169" t="n">
+        <v>44.98</v>
+      </c>
+      <c r="AN169" t="n">
+        <v>48.73</v>
       </c>
       <c r="AO169" t="inlineStr">
         <is>
@@ -73110,7 +72522,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr"/>
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>3297</t>
@@ -73294,15 +72710,11 @@
           <t>43.55</t>
         </is>
       </c>
-      <c r="AM170" t="inlineStr">
-        <is>
-          <t>45.16</t>
-        </is>
-      </c>
-      <c r="AN170" t="inlineStr">
-        <is>
-          <t>49.08</t>
-        </is>
+      <c r="AM170" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="AN170" t="n">
+        <v>49.08</v>
       </c>
       <c r="AO170" t="inlineStr">
         <is>
@@ -73538,7 +72950,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr"/>
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>3297</t>
@@ -73722,15 +73138,11 @@
           <t>43.86</t>
         </is>
       </c>
-      <c r="AM171" t="inlineStr">
-        <is>
-          <t>45.34</t>
-        </is>
-      </c>
-      <c r="AN171" t="inlineStr">
-        <is>
-          <t>49.43</t>
-        </is>
+      <c r="AM171" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="AN171" t="n">
+        <v>49.43</v>
       </c>
       <c r="AO171" t="inlineStr">
         <is>
@@ -73966,7 +73378,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr"/>
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>3297</t>
@@ -74150,15 +73566,11 @@
           <t>44.69</t>
         </is>
       </c>
-      <c r="AM172" t="inlineStr">
-        <is>
-          <t>45.59</t>
-        </is>
-      </c>
-      <c r="AN172" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
+      <c r="AM172" t="n">
+        <v>45.59</v>
+      </c>
+      <c r="AN172" t="n">
+        <v>49.8</v>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
@@ -74394,7 +73806,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr"/>
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>3297</t>
@@ -74578,15 +73994,11 @@
           <t>45.48</t>
         </is>
       </c>
-      <c r="AM173" t="inlineStr">
-        <is>
-          <t>45.77</t>
-        </is>
-      </c>
-      <c r="AN173" t="inlineStr">
-        <is>
-          <t>50.16</t>
-        </is>
+      <c r="AM173" t="n">
+        <v>45.77</v>
+      </c>
+      <c r="AN173" t="n">
+        <v>50.16</v>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
@@ -74822,7 +74234,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr"/>
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>3297</t>
@@ -75006,15 +74422,11 @@
           <t>45.41</t>
         </is>
       </c>
-      <c r="AM174" t="inlineStr">
-        <is>
-          <t>45.95</t>
-        </is>
-      </c>
-      <c r="AN174" t="inlineStr">
-        <is>
-          <t>50.5</t>
-        </is>
+      <c r="AM174" t="n">
+        <v>45.95</v>
+      </c>
+      <c r="AN174" t="n">
+        <v>50.5</v>
       </c>
       <c r="AO174" t="inlineStr">
         <is>
@@ -75250,7 +74662,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr"/>
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>3297</t>
@@ -75434,15 +74850,11 @@
           <t>44.92</t>
         </is>
       </c>
-      <c r="AM175" t="inlineStr">
-        <is>
-          <t>46.16</t>
-        </is>
-      </c>
-      <c r="AN175" t="inlineStr">
-        <is>
-          <t>50.86</t>
-        </is>
+      <c r="AM175" t="n">
+        <v>46.16</v>
+      </c>
+      <c r="AN175" t="n">
+        <v>50.86</v>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
@@ -75678,7 +75090,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr"/>
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>3297</t>
@@ -75862,15 +75278,11 @@
           <t>44.63</t>
         </is>
       </c>
-      <c r="AM176" t="inlineStr">
-        <is>
-          <t>46.4</t>
-        </is>
-      </c>
-      <c r="AN176" t="inlineStr">
-        <is>
-          <t>51.32</t>
-        </is>
+      <c r="AM176" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="AN176" t="n">
+        <v>51.32</v>
       </c>
       <c r="AO176" t="inlineStr">
         <is>
@@ -76106,7 +75518,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr"/>
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>3297</t>
@@ -76290,15 +75706,11 @@
           <t>44.1</t>
         </is>
       </c>
-      <c r="AM177" t="inlineStr">
-        <is>
-          <t>46.47</t>
-        </is>
-      </c>
-      <c r="AN177" t="inlineStr">
-        <is>
-          <t>51.6</t>
-        </is>
+      <c r="AM177" t="n">
+        <v>46.47</v>
+      </c>
+      <c r="AN177" t="n">
+        <v>51.6</v>
       </c>
       <c r="AO177" t="inlineStr">
         <is>
@@ -76720,15 +76132,11 @@
           <t>103.5</t>
         </is>
       </c>
-      <c r="AM178" t="inlineStr">
-        <is>
-          <t>103.36</t>
-        </is>
-      </c>
-      <c r="AN178" t="inlineStr">
-        <is>
-          <t>99.15</t>
-        </is>
+      <c r="AM178" t="n">
+        <v>103.36</v>
+      </c>
+      <c r="AN178" t="n">
+        <v>99.15000000000001</v>
       </c>
       <c r="AO178" t="inlineStr">
         <is>
@@ -77150,15 +76558,11 @@
           <t>104.1</t>
         </is>
       </c>
-      <c r="AM179" t="inlineStr">
-        <is>
-          <t>103.14</t>
-        </is>
-      </c>
-      <c r="AN179" t="inlineStr">
-        <is>
-          <t>98.92</t>
-        </is>
+      <c r="AM179" t="n">
+        <v>103.14</v>
+      </c>
+      <c r="AN179" t="n">
+        <v>98.92</v>
       </c>
       <c r="AO179" t="inlineStr">
         <is>
@@ -77580,15 +76984,11 @@
           <t>105.2</t>
         </is>
       </c>
-      <c r="AM180" t="inlineStr">
-        <is>
-          <t>103.14</t>
-        </is>
-      </c>
-      <c r="AN180" t="inlineStr">
-        <is>
-          <t>98.69</t>
-        </is>
+      <c r="AM180" t="n">
+        <v>103.14</v>
+      </c>
+      <c r="AN180" t="n">
+        <v>98.69</v>
       </c>
       <c r="AO180" t="inlineStr">
         <is>
@@ -78010,15 +77410,11 @@
           <t>105.2</t>
         </is>
       </c>
-      <c r="AM181" t="inlineStr">
-        <is>
-          <t>102.96</t>
-        </is>
-      </c>
-      <c r="AN181" t="inlineStr">
-        <is>
-          <t>98.3</t>
-        </is>
+      <c r="AM181" t="n">
+        <v>102.96</v>
+      </c>
+      <c r="AN181" t="n">
+        <v>98.3</v>
       </c>
       <c r="AO181" t="inlineStr">
         <is>
@@ -78440,15 +77836,11 @@
           <t>106.3</t>
         </is>
       </c>
-      <c r="AM182" t="inlineStr">
-        <is>
-          <t>103.11</t>
-        </is>
-      </c>
-      <c r="AN182" t="inlineStr">
-        <is>
-          <t>97.96</t>
-        </is>
+      <c r="AM182" t="n">
+        <v>103.11</v>
+      </c>
+      <c r="AN182" t="n">
+        <v>97.95999999999999</v>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
@@ -78870,15 +78262,11 @@
           <t>106.6</t>
         </is>
       </c>
-      <c r="AM183" t="inlineStr">
-        <is>
-          <t>103.48</t>
-        </is>
-      </c>
-      <c r="AN183" t="inlineStr">
-        <is>
-          <t>97.59</t>
-        </is>
+      <c r="AM183" t="n">
+        <v>103.48</v>
+      </c>
+      <c r="AN183" t="n">
+        <v>97.59</v>
       </c>
       <c r="AO183" t="inlineStr">
         <is>
@@ -79300,15 +78688,11 @@
           <t>107.0</t>
         </is>
       </c>
-      <c r="AM184" t="inlineStr">
-        <is>
-          <t>103.61</t>
-        </is>
-      </c>
-      <c r="AN184" t="inlineStr">
-        <is>
-          <t>97.13</t>
-        </is>
+      <c r="AM184" t="n">
+        <v>103.61</v>
+      </c>
+      <c r="AN184" t="n">
+        <v>97.13</v>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
@@ -79730,15 +79114,11 @@
           <t>106.0</t>
         </is>
       </c>
-      <c r="AM185" t="inlineStr">
-        <is>
-          <t>103.71</t>
-        </is>
-      </c>
-      <c r="AN185" t="inlineStr">
-        <is>
-          <t>96.71</t>
-        </is>
+      <c r="AM185" t="n">
+        <v>103.71</v>
+      </c>
+      <c r="AN185" t="n">
+        <v>96.70999999999999</v>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
@@ -80160,15 +79540,11 @@
           <t>104.44</t>
         </is>
       </c>
-      <c r="AM186" t="inlineStr">
-        <is>
-          <t>104.06</t>
-        </is>
-      </c>
-      <c r="AN186" t="inlineStr">
-        <is>
-          <t>96.26</t>
-        </is>
+      <c r="AM186" t="n">
+        <v>104.06</v>
+      </c>
+      <c r="AN186" t="n">
+        <v>96.26000000000001</v>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
@@ -80590,15 +79966,11 @@
           <t>102.92</t>
         </is>
       </c>
-      <c r="AM187" t="inlineStr">
-        <is>
-          <t>104.44</t>
-        </is>
-      </c>
-      <c r="AN187" t="inlineStr">
-        <is>
-          <t>95.81</t>
-        </is>
+      <c r="AM187" t="n">
+        <v>104.44</v>
+      </c>
+      <c r="AN187" t="n">
+        <v>95.81</v>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
@@ -81020,15 +80392,11 @@
           <t>101.94</t>
         </is>
       </c>
-      <c r="AM188" t="inlineStr">
-        <is>
-          <t>104.96</t>
-        </is>
-      </c>
-      <c r="AN188" t="inlineStr">
-        <is>
-          <t>95.43</t>
-        </is>
+      <c r="AM188" t="n">
+        <v>104.96</v>
+      </c>
+      <c r="AN188" t="n">
+        <v>95.43000000000001</v>
       </c>
       <c r="AO188" t="inlineStr">
         <is>
@@ -81266,7 +80634,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -81450,15 +80818,11 @@
           <t>45.66</t>
         </is>
       </c>
-      <c r="AM189" t="inlineStr">
-        <is>
-          <t>44.82</t>
-        </is>
-      </c>
-      <c r="AN189" t="inlineStr">
-        <is>
-          <t>47.03</t>
-        </is>
+      <c r="AM189" t="n">
+        <v>44.82</v>
+      </c>
+      <c r="AN189" t="n">
+        <v>47.03</v>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
@@ -81696,7 +81060,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -81880,15 +81244,11 @@
           <t>45.18</t>
         </is>
       </c>
-      <c r="AM190" t="inlineStr">
-        <is>
-          <t>44.73</t>
-        </is>
-      </c>
-      <c r="AN190" t="inlineStr">
-        <is>
-          <t>47.11</t>
-        </is>
+      <c r="AM190" t="n">
+        <v>44.73</v>
+      </c>
+      <c r="AN190" t="n">
+        <v>47.11</v>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
@@ -82126,7 +81486,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -82310,15 +81670,11 @@
           <t>44.95</t>
         </is>
       </c>
-      <c r="AM191" t="inlineStr">
-        <is>
-          <t>44.72</t>
-        </is>
-      </c>
-      <c r="AN191" t="inlineStr">
-        <is>
-          <t>47.21</t>
-        </is>
+      <c r="AM191" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="AN191" t="n">
+        <v>47.21</v>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
@@ -82556,7 +81912,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -82740,15 +82096,11 @@
           <t>44.88</t>
         </is>
       </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>44.68</t>
-        </is>
-      </c>
-      <c r="AN192" t="inlineStr">
-        <is>
-          <t>47.31</t>
-        </is>
+      <c r="AM192" t="n">
+        <v>44.68</v>
+      </c>
+      <c r="AN192" t="n">
+        <v>47.31</v>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
@@ -82986,7 +82338,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -83170,15 +82522,11 @@
           <t>45.1</t>
         </is>
       </c>
-      <c r="AM193" t="inlineStr">
-        <is>
-          <t>44.7</t>
-        </is>
-      </c>
-      <c r="AN193" t="inlineStr">
-        <is>
-          <t>47.41</t>
-        </is>
+      <c r="AM193" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="AN193" t="n">
+        <v>47.41</v>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
@@ -83416,7 +82764,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -83600,15 +82948,11 @@
           <t>45.38</t>
         </is>
       </c>
-      <c r="AM194" t="inlineStr">
-        <is>
-          <t>44.76</t>
-        </is>
-      </c>
-      <c r="AN194" t="inlineStr">
-        <is>
-          <t>47.53</t>
-        </is>
+      <c r="AM194" t="n">
+        <v>44.76</v>
+      </c>
+      <c r="AN194" t="n">
+        <v>47.53</v>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
@@ -83846,7 +83190,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -84030,15 +83374,11 @@
           <t>45.37</t>
         </is>
       </c>
-      <c r="AM195" t="inlineStr">
-        <is>
-          <t>44.88</t>
-        </is>
-      </c>
-      <c r="AN195" t="inlineStr">
-        <is>
-          <t>47.68</t>
-        </is>
+      <c r="AM195" t="n">
+        <v>44.88</v>
+      </c>
+      <c r="AN195" t="n">
+        <v>47.68</v>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
@@ -84274,7 +83614,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr"/>
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>1583</t>
@@ -84456,15 +83800,11 @@
           <t>44.7</t>
         </is>
       </c>
-      <c r="AM196" t="inlineStr">
-        <is>
-          <t>44.98</t>
-        </is>
-      </c>
-      <c r="AN196" t="inlineStr">
-        <is>
-          <t>47.79</t>
-        </is>
+      <c r="AM196" t="n">
+        <v>44.98</v>
+      </c>
+      <c r="AN196" t="n">
+        <v>47.79</v>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
@@ -84700,7 +84040,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr"/>
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>1583</t>
@@ -84882,15 +84226,11 @@
           <t>44.14</t>
         </is>
       </c>
-      <c r="AM197" t="inlineStr">
-        <is>
-          <t>45.08</t>
-        </is>
-      </c>
-      <c r="AN197" t="inlineStr">
-        <is>
-          <t>47.9</t>
-        </is>
+      <c r="AM197" t="n">
+        <v>45.08</v>
+      </c>
+      <c r="AN197" t="n">
+        <v>47.9</v>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
@@ -85126,7 +84466,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr"/>
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>1583</t>
@@ -85308,15 +84652,11 @@
           <t>43.73999999999999</t>
         </is>
       </c>
-      <c r="AM198" t="inlineStr">
-        <is>
-          <t>45.18</t>
-        </is>
-      </c>
-      <c r="AN198" t="inlineStr">
-        <is>
-          <t>48.0</t>
-        </is>
+      <c r="AM198" t="n">
+        <v>45.18</v>
+      </c>
+      <c r="AN198" t="n">
+        <v>48</v>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
@@ -85738,15 +85078,11 @@
           <t>43.59</t>
         </is>
       </c>
-      <c r="AM199" t="inlineStr">
-        <is>
-          <t>45.31</t>
-        </is>
-      </c>
-      <c r="AN199" t="inlineStr">
-        <is>
-          <t>48.11</t>
-        </is>
+      <c r="AM199" t="n">
+        <v>45.31</v>
+      </c>
+      <c r="AN199" t="n">
+        <v>48.11</v>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
@@ -86169,15 +85505,11 @@
           <t>18.13</t>
         </is>
       </c>
-      <c r="AM200" t="inlineStr">
-        <is>
-          <t>17.65</t>
-        </is>
-      </c>
-      <c r="AN200" t="inlineStr">
-        <is>
-          <t>17.53</t>
-        </is>
+      <c r="AM200" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="AN200" t="n">
+        <v>17.53</v>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
@@ -86600,15 +85932,11 @@
           <t>18.03</t>
         </is>
       </c>
-      <c r="AM201" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
-      </c>
-      <c r="AN201" t="inlineStr">
-        <is>
-          <t>17.51</t>
-        </is>
+      <c r="AM201" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="AN201" t="n">
+        <v>17.51</v>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
@@ -87031,15 +86359,11 @@
           <t>17.93</t>
         </is>
       </c>
-      <c r="AM202" t="inlineStr">
-        <is>
-          <t>17.57</t>
-        </is>
-      </c>
-      <c r="AN202" t="inlineStr">
-        <is>
-          <t>17.5</t>
-        </is>
+      <c r="AM202" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="AN202" t="n">
+        <v>17.5</v>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
@@ -87462,15 +86786,11 @@
           <t>17.79</t>
         </is>
       </c>
-      <c r="AM203" t="inlineStr">
-        <is>
-          <t>17.53</t>
-        </is>
-      </c>
-      <c r="AN203" t="inlineStr">
-        <is>
-          <t>17.48</t>
-        </is>
+      <c r="AM203" t="n">
+        <v>17.53</v>
+      </c>
+      <c r="AN203" t="n">
+        <v>17.48</v>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
@@ -87893,15 +87213,11 @@
           <t>17.72</t>
         </is>
       </c>
-      <c r="AM204" t="inlineStr">
-        <is>
-          <t>17.5</t>
-        </is>
-      </c>
-      <c r="AN204" t="inlineStr">
-        <is>
-          <t>17.48</t>
-        </is>
+      <c r="AM204" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AN204" t="n">
+        <v>17.48</v>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
@@ -88324,15 +87640,11 @@
           <t>17.66</t>
         </is>
       </c>
-      <c r="AM205" t="inlineStr">
-        <is>
-          <t>17.48</t>
-        </is>
-      </c>
-      <c r="AN205" t="inlineStr">
-        <is>
-          <t>17.47</t>
-        </is>
+      <c r="AM205" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="AN205" t="n">
+        <v>17.47</v>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
@@ -88755,15 +88067,11 @@
           <t>17.8</t>
         </is>
       </c>
-      <c r="AM206" t="inlineStr">
-        <is>
-          <t>17.46</t>
-        </is>
-      </c>
-      <c r="AN206" t="inlineStr">
-        <is>
-          <t>17.46</t>
-        </is>
+      <c r="AM206" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="AN206" t="n">
+        <v>17.46</v>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
@@ -89001,7 +88309,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -89186,15 +88494,11 @@
           <t>17.69</t>
         </is>
       </c>
-      <c r="AM207" t="inlineStr">
-        <is>
-          <t>17.44</t>
-        </is>
-      </c>
-      <c r="AN207" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
+      <c r="AM207" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="AN207" t="n">
+        <v>17.45</v>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
@@ -89432,7 +88736,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -89617,15 +88921,11 @@
           <t>17.6</t>
         </is>
       </c>
-      <c r="AM208" t="inlineStr">
-        <is>
-          <t>17.44</t>
-        </is>
-      </c>
-      <c r="AN208" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
+      <c r="AM208" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="AN208" t="n">
+        <v>17.45</v>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
@@ -89863,7 +89163,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -90048,15 +89348,11 @@
           <t>17.5</t>
         </is>
       </c>
-      <c r="AM209" t="inlineStr">
-        <is>
-          <t>17.44</t>
-        </is>
-      </c>
-      <c r="AN209" t="inlineStr">
-        <is>
-          <t>17.44</t>
-        </is>
+      <c r="AM209" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="AN209" t="n">
+        <v>17.44</v>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
@@ -90294,7 +89590,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -90479,15 +89775,11 @@
           <t>17.45</t>
         </is>
       </c>
-      <c r="AM210" t="inlineStr">
-        <is>
-          <t>17.44</t>
-        </is>
-      </c>
-      <c r="AN210" t="inlineStr">
-        <is>
-          <t>17.44</t>
-        </is>
+      <c r="AM210" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="AN210" t="n">
+        <v>17.44</v>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
@@ -90912,15 +90204,11 @@
           <t>71.02</t>
         </is>
       </c>
-      <c r="AM211" t="inlineStr">
-        <is>
-          <t>67.25</t>
-        </is>
-      </c>
-      <c r="AN211" t="inlineStr">
-        <is>
-          <t>61.0</t>
-        </is>
+      <c r="AM211" t="n">
+        <v>67.25</v>
+      </c>
+      <c r="AN211" t="n">
+        <v>61</v>
       </c>
       <c r="AO211" t="inlineStr">
         <is>
@@ -91345,15 +90633,11 @@
           <t>70.83999999999999</t>
         </is>
       </c>
-      <c r="AM212" t="inlineStr">
-        <is>
-          <t>66.73</t>
-        </is>
-      </c>
-      <c r="AN212" t="inlineStr">
-        <is>
-          <t>60.67</t>
-        </is>
+      <c r="AM212" t="n">
+        <v>66.73</v>
+      </c>
+      <c r="AN212" t="n">
+        <v>60.67</v>
       </c>
       <c r="AO212" t="inlineStr">
         <is>
@@ -91778,15 +91062,11 @@
           <t>70.74</t>
         </is>
       </c>
-      <c r="AM213" t="inlineStr">
-        <is>
-          <t>66.16</t>
-        </is>
-      </c>
-      <c r="AN213" t="inlineStr">
-        <is>
-          <t>60.35</t>
-        </is>
+      <c r="AM213" t="n">
+        <v>66.16</v>
+      </c>
+      <c r="AN213" t="n">
+        <v>60.35</v>
       </c>
       <c r="AO213" t="inlineStr">
         <is>
@@ -92211,15 +91491,11 @@
           <t>70.94</t>
         </is>
       </c>
-      <c r="AM214" t="inlineStr">
-        <is>
-          <t>65.37</t>
-        </is>
-      </c>
-      <c r="AN214" t="inlineStr">
-        <is>
-          <t>60.02</t>
-        </is>
+      <c r="AM214" t="n">
+        <v>65.37</v>
+      </c>
+      <c r="AN214" t="n">
+        <v>60.02</v>
       </c>
       <c r="AO214" t="inlineStr">
         <is>
@@ -92644,15 +91920,11 @@
           <t>71.24</t>
         </is>
       </c>
-      <c r="AM215" t="inlineStr">
-        <is>
-          <t>64.55</t>
-        </is>
-      </c>
-      <c r="AN215" t="inlineStr">
-        <is>
-          <t>59.7</t>
-        </is>
+      <c r="AM215" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="AN215" t="n">
+        <v>59.7</v>
       </c>
       <c r="AO215" t="inlineStr">
         <is>
@@ -93077,15 +92349,11 @@
           <t>72.03999999999999</t>
         </is>
       </c>
-      <c r="AM216" t="inlineStr">
-        <is>
-          <t>63.87</t>
-        </is>
-      </c>
-      <c r="AN216" t="inlineStr">
-        <is>
-          <t>59.37</t>
-        </is>
+      <c r="AM216" t="n">
+        <v>63.87</v>
+      </c>
+      <c r="AN216" t="n">
+        <v>59.37</v>
       </c>
       <c r="AO216" t="inlineStr">
         <is>
@@ -93510,15 +92778,11 @@
           <t>71.35999999999999</t>
         </is>
       </c>
-      <c r="AM217" t="inlineStr">
-        <is>
-          <t>63.16</t>
-        </is>
-      </c>
-      <c r="AN217" t="inlineStr">
-        <is>
-          <t>59.02</t>
-        </is>
+      <c r="AM217" t="n">
+        <v>63.16</v>
+      </c>
+      <c r="AN217" t="n">
+        <v>59.02</v>
       </c>
       <c r="AO217" t="inlineStr">
         <is>
@@ -93943,15 +93207,11 @@
           <t>70.1</t>
         </is>
       </c>
-      <c r="AM218" t="inlineStr">
-        <is>
-          <t>62.59</t>
-        </is>
-      </c>
-      <c r="AN218" t="inlineStr">
-        <is>
-          <t>58.66</t>
-        </is>
+      <c r="AM218" t="n">
+        <v>62.59</v>
+      </c>
+      <c r="AN218" t="n">
+        <v>58.66</v>
       </c>
       <c r="AO218" t="inlineStr">
         <is>
@@ -94376,15 +93636,11 @@
           <t>68.56</t>
         </is>
       </c>
-      <c r="AM219" t="inlineStr">
-        <is>
-          <t>61.88</t>
-        </is>
-      </c>
-      <c r="AN219" t="inlineStr">
-        <is>
-          <t>58.26</t>
-        </is>
+      <c r="AM219" t="n">
+        <v>61.88</v>
+      </c>
+      <c r="AN219" t="n">
+        <v>58.26</v>
       </c>
       <c r="AO219" t="inlineStr">
         <is>
@@ -94809,15 +94065,11 @@
           <t>66.9</t>
         </is>
       </c>
-      <c r="AM220" t="inlineStr">
-        <is>
-          <t>61.15</t>
-        </is>
-      </c>
-      <c r="AN220" t="inlineStr">
-        <is>
-          <t>57.87</t>
-        </is>
+      <c r="AM220" t="n">
+        <v>61.15</v>
+      </c>
+      <c r="AN220" t="n">
+        <v>57.87</v>
       </c>
       <c r="AO220" t="inlineStr">
         <is>
@@ -95242,15 +94494,11 @@
           <t>64.8</t>
         </is>
       </c>
-      <c r="AM221" t="inlineStr">
-        <is>
-          <t>60.52</t>
-        </is>
-      </c>
-      <c r="AN221" t="inlineStr">
-        <is>
-          <t>57.46</t>
-        </is>
+      <c r="AM221" t="n">
+        <v>60.52</v>
+      </c>
+      <c r="AN221" t="n">
+        <v>57.46</v>
       </c>
       <c r="AO221" t="inlineStr">
         <is>
